--- a/工厂配送兔司家门店月度销售报表_格式化模板.xlsx
+++ b/工厂配送兔司家门店月度销售报表_格式化模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wadec\Documents\projects\mainyan-auto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F127602-2E5F-4108-B269-728895ECB2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6ACE02-A753-4C25-BE69-AB446186779A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="配送门店业绩表 5.1-5.31" sheetId="4" r:id="rId1"/>
@@ -846,7 +846,7 @@
     <col min="11" max="11" width="6.6640625" style="9" customWidth="1"/>
     <col min="12" max="12" width="6.21875" style="9" customWidth="1"/>
     <col min="13" max="13" width="7.21875" style="9" customWidth="1"/>
-    <col min="14" max="14" width="10.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.21875" style="9" customWidth="1"/>
     <col min="15" max="15" width="9.109375" style="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="8.88671875" style="9" customWidth="1"/>
     <col min="17" max="17" width="9" style="9"/>
